--- a/laborator8_students.xlsx
+++ b/laborator8_students.xlsx
@@ -146,7 +146,7 @@
         <v>234.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="4">
@@ -163,7 +163,7 @@
         <v>213.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="5">
